--- a/data/trans_orig/P78A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P78A_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si la persona sustentadora principal ha trabajado anteriormente en 2023</t>
+          <t>Población según si la persona sustentadora principal ha trabajado anteriormente en 2023 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>372072</t>
+          <t>371694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>380633</t>
+          <t>380729</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>531007</t>
+          <t>531544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>563715</t>
+          <t>563314</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>906713</t>
+          <t>908713</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>941800</t>
+          <t>943342</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,04%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>11142</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>112864</t>
+          <t>113265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>145572</t>
+          <t>145035</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>117615</t>
+          <t>116073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>152702</t>
+          <t>150702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,23%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>656601</t>
+          <t>654882</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>739803</t>
+          <t>738391</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>942462</t>
+          <t>938607</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1141124</t>
+          <t>1135337</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1637697</t>
+          <t>1628371</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1847216</t>
+          <t>1852755</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,15%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>162293</t>
+          <t>163705</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>245495</t>
+          <t>247214</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>158445</t>
+          <t>164232</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>357107</t>
+          <t>360962</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354449</t>
+          <t>348910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>563968</t>
+          <t>573294</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>26,04%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>157912</t>
+          <t>158141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182305</t>
+          <t>182224</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>172155</t>
+          <t>172253</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195645</t>
+          <t>195678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>77,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>338561</t>
+          <t>338003</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>372714</t>
+          <t>372461</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>13600</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37912</t>
+          <t>37683</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26963</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50453</t>
+          <t>50355</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45718</t>
+          <t>45971</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>79871</t>
+          <t>80429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1202694</t>
+          <t>1200852</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1292991</t>
+          <t>1297056</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1678652</t>
+          <t>1681612</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1867406</t>
+          <t>1866005</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2919635</t>
+          <t>2918030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3114518</t>
+          <t>3112203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,58%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>187765</t>
+          <t>183700</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>278062</t>
+          <t>279904</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>331350</t>
+          <t>332751</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>520104</t>
+          <t>517144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>564994</t>
+          <t>567309</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>759877</t>
+          <t>761482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P78A_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P78A_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>377681</t>
+          <t>409191</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>371694</t>
+          <t>403086</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>380729</t>
+          <t>412270</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>547822</t>
+          <t>597952</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>531544</t>
+          <t>581025</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>563314</t>
+          <t>615211</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>925503</t>
+          <t>1007143</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>908713</t>
+          <t>987766</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>943342</t>
+          <t>1026181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,08%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5404</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>11509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>128757</t>
+          <t>139448</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113265</t>
+          <t>122189</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>145035</t>
+          <t>156375</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>133912</t>
+          <t>144852</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>116073</t>
+          <t>125814</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>150702</t>
+          <t>164229</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>382836</t>
+          <t>414595</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>382836</t>
+          <t>414595</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>382836</t>
+          <t>414595</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>676579</t>
+          <t>737400</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>676579</t>
+          <t>737400</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>676579</t>
+          <t>737400</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1059415</t>
+          <t>1151995</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1059415</t>
+          <t>1151995</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1059415</t>
+          <t>1151995</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>699384</t>
+          <t>755760</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>654882</t>
+          <t>717528</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>738391</t>
+          <t>793310</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1007515</t>
+          <t>891201</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>938607</t>
+          <t>856556</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1135337</t>
+          <t>920424</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1706899</t>
+          <t>1646961</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1628371</t>
+          <t>1595635</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1852755</t>
+          <t>1697395</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>202712</t>
+          <t>196606</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>163705</t>
+          <t>159056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247214</t>
+          <t>234838</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>292054</t>
+          <t>340628</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164232</t>
+          <t>311405</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>360962</t>
+          <t>375273</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>494766</t>
+          <t>537234</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348910</t>
+          <t>486800</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>573294</t>
+          <t>588560</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,95%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>902096</t>
+          <t>952366</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>902096</t>
+          <t>952366</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>902096</t>
+          <t>952366</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1299569</t>
+          <t>1231829</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1299569</t>
+          <t>1231829</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1299569</t>
+          <t>1231829</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2201665</t>
+          <t>2184195</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2201665</t>
+          <t>2184195</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2201665</t>
+          <t>2184195</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>172112</t>
+          <t>192937</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158141</t>
+          <t>176225</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182224</t>
+          <t>204194</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>184937</t>
+          <t>211015</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>172253</t>
+          <t>196614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>195678</t>
+          <t>222186</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>357049</t>
+          <t>403952</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>338003</t>
+          <t>383114</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>372461</t>
+          <t>419897</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,59%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23712</t>
+          <t>26942</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13600</t>
+          <t>15685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37683</t>
+          <t>43654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37671</t>
+          <t>43102</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26930</t>
+          <t>31931</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50355</t>
+          <t>57503</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>61383</t>
+          <t>70044</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45971</t>
+          <t>54099</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80429</t>
+          <t>90882</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,17%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>195824</t>
+          <t>219879</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>195824</t>
+          <t>219879</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>195824</t>
+          <t>219879</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>222608</t>
+          <t>254117</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>222608</t>
+          <t>254117</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>222608</t>
+          <t>254117</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>418432</t>
+          <t>473996</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>418432</t>
+          <t>473996</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>418432</t>
+          <t>473996</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1249177</t>
+          <t>1357888</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1200852</t>
+          <t>1314042</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1297056</t>
+          <t>1396273</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1740273</t>
+          <t>1700168</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1681612</t>
+          <t>1663196</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1866005</t>
+          <t>1742259</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>78,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2989451</t>
+          <t>3058056</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2918030</t>
+          <t>2992563</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3112203</t>
+          <t>3109600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>81,61%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>231579</t>
+          <t>228952</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183700</t>
+          <t>190567</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>279904</t>
+          <t>272798</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>458483</t>
+          <t>523178</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>332751</t>
+          <t>481087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>517144</t>
+          <t>560150</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>25,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>690061</t>
+          <t>752130</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>567309</t>
+          <t>700586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>761482</t>
+          <t>817623</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1480756</t>
+          <t>1586840</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1480756</t>
+          <t>1586840</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1480756</t>
+          <t>1586840</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2198756</t>
+          <t>2223346</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2198756</t>
+          <t>2223346</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2198756</t>
+          <t>2223346</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>3679512</t>
+          <t>3810186</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3679512</t>
+          <t>3810186</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>3679512</t>
+          <t>3810186</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
